--- a/artfynd/A 31835-2024 artfynd.xlsx
+++ b/artfynd/A 31835-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2883,7 +2883,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>74945924</v>
+        <v>74945884</v>
       </c>
       <c r="B21" t="n">
         <v>77506</v>
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>356276.8155853078</v>
+        <v>356528.7844578259</v>
       </c>
       <c r="R21" t="n">
-        <v>6743903.033251501</v>
+        <v>6743767.815317962</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3000,7 +3000,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>74945884</v>
+        <v>74945908</v>
       </c>
       <c r="B22" t="n">
         <v>77506</v>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>356528.7844578259</v>
+        <v>356312.2189784987</v>
       </c>
       <c r="R22" t="n">
-        <v>6743767.815317962</v>
+        <v>6743664.149202798</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>74945908</v>
+        <v>74946029</v>
       </c>
       <c r="B23" t="n">
         <v>77506</v>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>356312.2189784987</v>
+        <v>356668.0393545362</v>
       </c>
       <c r="R23" t="n">
-        <v>6743664.149202798</v>
+        <v>6744018.234539317</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>74946029</v>
+        <v>74946035</v>
       </c>
       <c r="B24" t="n">
         <v>77506</v>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>356668.0393545362</v>
+        <v>356653.18672644</v>
       </c>
       <c r="R24" t="n">
-        <v>6744018.234539317</v>
+        <v>6744013.945557805</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3351,7 +3351,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>74946035</v>
+        <v>74945920</v>
       </c>
       <c r="B25" t="n">
         <v>77506</v>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>356653.18672644</v>
+        <v>356241.0542523232</v>
       </c>
       <c r="R25" t="n">
-        <v>6744013.945557805</v>
+        <v>6743914.245372762</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>74945920</v>
+        <v>74946027</v>
       </c>
       <c r="B26" t="n">
         <v>77506</v>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>356241.0542523232</v>
+        <v>356689.1060339456</v>
       </c>
       <c r="R26" t="n">
-        <v>6743914.245372762</v>
+        <v>6744018.85407682</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3585,7 +3585,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>74946027</v>
+        <v>74945934</v>
       </c>
       <c r="B27" t="n">
         <v>77506</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>356689.1060339456</v>
+        <v>356313.1172921766</v>
       </c>
       <c r="R27" t="n">
-        <v>6744018.85407682</v>
+        <v>6743953.849163152</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3702,7 +3702,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>74945934</v>
+        <v>74945874</v>
       </c>
       <c r="B28" t="n">
         <v>77506</v>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>356313.1172921766</v>
+        <v>356591.24416596</v>
       </c>
       <c r="R28" t="n">
-        <v>6743953.849163152</v>
+        <v>6743751.135459653</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3819,7 +3819,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>74945874</v>
+        <v>74945870</v>
       </c>
       <c r="B29" t="n">
         <v>77506</v>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>356591.24416596</v>
+        <v>356593.1186530608</v>
       </c>
       <c r="R29" t="n">
-        <v>6743751.135459653</v>
+        <v>6743736.890759191</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3936,7 +3936,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>74945870</v>
+        <v>74945886</v>
       </c>
       <c r="B30" t="n">
         <v>77506</v>
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>356593.1186530608</v>
+        <v>356523.9377770555</v>
       </c>
       <c r="R30" t="n">
-        <v>6743736.890759191</v>
+        <v>6743768.987367193</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4053,7 +4053,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>74945886</v>
+        <v>74946033</v>
       </c>
       <c r="B31" t="n">
         <v>77506</v>
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>356523.9377770555</v>
+        <v>356651.8778176149</v>
       </c>
       <c r="R31" t="n">
-        <v>6743768.987367193</v>
+        <v>6744017.906630695</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>74946033</v>
+        <v>74946031</v>
       </c>
       <c r="B32" t="n">
         <v>77506</v>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>356651.8778176149</v>
+        <v>356663.2125754335</v>
       </c>
       <c r="R32" t="n">
-        <v>6744017.906630695</v>
+        <v>6744019.8941071</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4287,7 +4287,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>74946031</v>
+        <v>74945917</v>
       </c>
       <c r="B33" t="n">
         <v>77506</v>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>356663.2125754335</v>
+        <v>356213.056936331</v>
       </c>
       <c r="R33" t="n">
-        <v>6744019.8941071</v>
+        <v>6743863.094878701</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>74945917</v>
+        <v>74946040</v>
       </c>
       <c r="B34" t="n">
         <v>77506</v>
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>356213.056936331</v>
+        <v>356625.0240124529</v>
       </c>
       <c r="R34" t="n">
-        <v>6743863.094878701</v>
+        <v>6743995.045933632</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4521,7 +4521,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>74946040</v>
+        <v>74945931</v>
       </c>
       <c r="B35" t="n">
         <v>77506</v>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>356625.0240124529</v>
+        <v>356290.91068178</v>
       </c>
       <c r="R35" t="n">
-        <v>6743995.045933632</v>
+        <v>6743924.940260041</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4638,7 +4638,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>74945931</v>
+        <v>74945943</v>
       </c>
       <c r="B36" t="n">
         <v>77506</v>
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>356290.91068178</v>
+        <v>356292.1926411735</v>
       </c>
       <c r="R36" t="n">
-        <v>6743924.940260041</v>
+        <v>6743981.074700621</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4755,7 +4755,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>74945943</v>
+        <v>74945913</v>
       </c>
       <c r="B37" t="n">
         <v>77506</v>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>356292.1926411735</v>
+        <v>356225.0552023668</v>
       </c>
       <c r="R37" t="n">
-        <v>6743981.074700621</v>
+        <v>6743857.236982612</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4872,7 +4872,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>74945913</v>
+        <v>74945888</v>
       </c>
       <c r="B38" t="n">
         <v>77506</v>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>356225.0552023668</v>
+        <v>356491.7761818137</v>
       </c>
       <c r="R38" t="n">
-        <v>6743857.236982612</v>
+        <v>6743687.218143881</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4989,7 +4989,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>74945888</v>
+        <v>74945912</v>
       </c>
       <c r="B39" t="n">
         <v>77506</v>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>356491.7761818137</v>
+        <v>356287.8627110944</v>
       </c>
       <c r="R39" t="n">
-        <v>6743687.218143881</v>
+        <v>6743739.887045127</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>74945912</v>
+        <v>74945936</v>
       </c>
       <c r="B40" t="n">
         <v>77506</v>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>356287.8627110944</v>
+        <v>356309.7759014289</v>
       </c>
       <c r="R40" t="n">
-        <v>6743739.887045127</v>
+        <v>6743955.93800684</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>74945936</v>
+        <v>74945876</v>
       </c>
       <c r="B41" t="n">
         <v>77506</v>
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>356309.7759014289</v>
+        <v>356575.2397760584</v>
       </c>
       <c r="R41" t="n">
-        <v>6743955.93800684</v>
+        <v>6743766.925155302</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5340,7 +5340,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>74945938</v>
+        <v>74945922</v>
       </c>
       <c r="B42" t="n">
         <v>77506</v>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>356298.796785888</v>
+        <v>356267.1030794847</v>
       </c>
       <c r="R42" t="n">
-        <v>6743974.945887225</v>
+        <v>6743904.890189095</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5454,240 +5454,6 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>74945876</v>
-      </c>
-      <c r="B43" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Rajmyren, Vrm</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>356575.2397760584</v>
-      </c>
-      <c r="R43" t="n">
-        <v>6743766.925155302</v>
-      </c>
-      <c r="S43" t="n">
-        <v>5</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Torsby</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Södra Finnskoga</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Garnlavsdraperier på gammeltall</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Per Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Per Gustafsson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>74945922</v>
-      </c>
-      <c r="B44" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Rajmyren, Vrm</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>356267.1030794847</v>
-      </c>
-      <c r="R44" t="n">
-        <v>6743904.890189095</v>
-      </c>
-      <c r="S44" t="n">
-        <v>5</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Torsby</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Södra Finnskoga</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Garnlavsdraperier på gammeltall</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Per Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Per Gustafsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
